--- a/PCB Cyclone I/PCB V2.1/BOM PPU_LITE.xlsx
+++ b/PCB Cyclone I/PCB V2.1/BOM PPU_LITE.xlsx
@@ -4952,7 +4952,7 @@
         <v>23</v>
       </c>
       <c r="D18" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" s="34" t="s">
         <v>69</v>
@@ -5171,7 +5171,7 @@
         <v>29</v>
       </c>
       <c r="D25" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>59</v>
